--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 41 个文件；主交付物 1 份 · 电子附件 4 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
+          <t>共 48 个文件；主交付物 1 份 · 电子附件 11 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
         </is>
       </c>
     </row>
@@ -562,24 +562,20 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>100 KB</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>高风险小区评分全量清单（772 个参评小区）</t>
-        </is>
-      </c>
+          <t>1856 KB</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -588,24 +584,20 @@
       <c r="B7" s="4" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>42 KB</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
-        </is>
-      </c>
+          <t>1606 KB</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -614,24 +606,20 @@
       <c r="B8" s="4" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>26 KB</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
-        </is>
-      </c>
+          <t>1546 KB</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -640,54 +628,42 @@
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>课题成果汇编-书籍封面.png</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>课题成果汇编-书籍封面.png</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>8 KB</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>交付物清单（本表）</t>
-        </is>
-      </c>
+          <t>1622 KB</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>过程成果报告</t>
-        </is>
-      </c>
+      <c r="B10" s="4" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>课题成果汇编-书脊.png</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>课题成果汇编-书脊.png</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
-        </is>
-      </c>
+          <t>43 KB</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -696,24 +672,20 @@
       <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>课题成果汇编-全封展开图.png</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>课题成果汇编-全封展开图.png</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
-        </is>
-      </c>
+          <t>3665 KB</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -722,24 +694,20 @@
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>天平街道住宅小区2025年度分析报告.docx</t>
+          <t>课题成果汇编-封底.png</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
+          <t>课题成果汇编-封底.png</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>217 KB</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
-        </is>
-      </c>
+          <t>1891 KB</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -748,22 +716,22 @@
       <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>289 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>高风险小区评分全量清单（772 个参评小区）</t>
         </is>
       </c>
     </row>
@@ -774,22 +742,22 @@
       <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>307 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
         </is>
       </c>
     </row>
@@ -800,22 +768,22 @@
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
         </is>
       </c>
     </row>
@@ -826,22 +794,22 @@
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>294 KB</t>
+          <t>8 KB</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>交付物清单（本表）</t>
         </is>
       </c>
     </row>
@@ -849,20 +817,24 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>过程成果报告</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>186 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -878,17 +850,17 @@
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>291 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -904,17 +876,17 @@
       <c r="B19" s="4" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>301 KB</t>
+          <t>217 KB</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -930,17 +902,17 @@
       <c r="B20" s="4" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
+          <t>289 KB</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -956,17 +928,17 @@
       <c r="B21" s="4" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>309 KB</t>
+          <t>307 KB</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -982,12 +954,12 @@
       <c r="B22" s="4" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1008,17 +980,17 @@
       <c r="B23" s="4" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>273 KB</t>
+          <t>294 KB</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1034,17 +1006,17 @@
       <c r="B24" s="4" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>271 KB</t>
+          <t>186 KB</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1060,22 +1032,22 @@
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>20260430 钦州路111弄工单分析报告.docx</t>
+          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
+          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>250 KB</t>
+          <t>291 KB</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1086,22 +1058,22 @@
       <c r="B26" s="4" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>478 KB</t>
+          <t>301 KB</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1112,22 +1084,22 @@
       <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>626 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1110,22 @@
       <c r="B28" s="4" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>104 KB</t>
+          <t>309 KB</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1164,22 +1136,22 @@
       <c r="B29" s="4" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>122 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1190,22 +1162,22 @@
       <c r="B30" s="4" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>117 KB</t>
+          <t>273 KB</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1216,22 +1188,22 @@
       <c r="B31" s="4" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>165 KB</t>
+          <t>271 KB</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1242,17 +1214,17 @@
       <c r="B32" s="4" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>250 KB</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1268,17 +1240,17 @@
       <c r="B33" s="4" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>478 KB</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1294,17 +1266,17 @@
       <c r="B34" s="4" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1343 KB</t>
+          <t>626 KB</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1320,17 +1292,17 @@
       <c r="B35" s="4" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>104 KB</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1346,17 +1318,17 @@
       <c r="B36" s="4" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>122 KB</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1372,17 +1344,17 @@
       <c r="B37" s="4" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>117 KB</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1398,17 +1370,17 @@
       <c r="B38" s="4" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>323 KB</t>
+          <t>165 KB</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1424,17 +1396,17 @@
       <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
+          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
+          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>127 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -1450,17 +1422,17 @@
       <c r="B40" s="4" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
+          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
+          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>102 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1476,17 +1448,17 @@
       <c r="B41" s="4" t="inlineStr"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
+          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
+          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>59 KB</t>
+          <t>1343 KB</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1502,17 +1474,17 @@
       <c r="B42" s="4" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2026年7月徐汇区12345工单分析报告.docx</t>
+          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
+          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>102 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1528,17 +1500,17 @@
       <c r="B43" s="4" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1445 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -1551,29 +1523,25 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>历史版本</t>
-        </is>
-      </c>
+      <c r="B44" s="4" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>12256 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>过程版本留档，非最终交付版本</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1584,20 +1552,206 @@
       <c r="B45" s="4" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
+          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>323 KB</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>127 KB</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>102 KB</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>59 KB</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>2026年7月徐汇区12345工单分析报告.docx</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>102 KB</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>1445 KB</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>月度滚动分析成果（19 份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>历史版本</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>12256 KB</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>过程版本留档，非最终交付版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
           <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>10289 KB</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>过程版本留档，非最终交付版本</t>
         </is>

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 48 个文件；主交付物 1 份 · 电子附件 11 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
+          <t>共 48 个文件；主交付物 1 份 · 电子附件 4 份 · 装帧素材 7 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
         </is>
       </c>
     </row>
@@ -562,20 +562,24 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1856 KB</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
+          <t>100 KB</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>高风险小区评分全量清单（772 个参评小区）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -584,20 +588,24 @@
       <c r="B7" s="4" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1606 KB</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>42 KB</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -606,20 +614,24 @@
       <c r="B8" s="4" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1546 KB</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>26 KB</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -628,42 +640,54 @@
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书籍封面.png</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书籍封面.png</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1622 KB</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>8 KB</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>交付物清单（本表）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>装帧素材</t>
+        </is>
+      </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书脊.png</t>
+          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书脊.png</t>
+          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>43 KB</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t>1856 KB</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>封面候选底图（非最终交付版本）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -672,20 +696,24 @@
       <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-全封展开图.png</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-全封展开图.png</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>3665 KB</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr"/>
+          <t>1606 KB</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>封面候选底图（非最终交付版本）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -694,20 +722,24 @@
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-封底.png</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-封底.png</t>
+          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1891 KB</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>1546 KB</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>封面候选底图（非最终交付版本）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -716,22 +748,22 @@
       <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>课题成果汇编-书籍封面.png</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>装订打印封面/课题成果汇编-书籍封面.png</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>1622 KB</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>高风险小区评分全量清单（772 个参评小区）</t>
+          <t>书籍装订印刷素材</t>
         </is>
       </c>
     </row>
@@ -742,22 +774,22 @@
       <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>课题成果汇编-书脊.png</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>装订打印封面/课题成果汇编-书脊.png</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>43 KB</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
+          <t>书籍装订印刷素材</t>
         </is>
       </c>
     </row>
@@ -768,22 +800,22 @@
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>课题成果汇编-全封展开图.png</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>装订打印封面/课题成果汇编-全封展开图.png</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>3681 KB</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
+          <t>书籍装订印刷素材</t>
         </is>
       </c>
     </row>
@@ -794,22 +826,22 @@
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>课题成果汇编-封底.png</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>装订打印封面/课题成果汇编-封底.png</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>8 KB</t>
+          <t>1895 KB</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>交付物清单（本表）</t>
+          <t>书籍装订印刷素材</t>
         </is>
       </c>
     </row>

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 48 个文件；主交付物 1 份 · 电子附件 4 份 · 装帧素材 7 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
+          <t>共 41 个文件；主交付物 1 份 · 电子附件 4 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>10316 KB</t>
+          <t>10317 KB</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -665,27 +665,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>装帧素材</t>
+          <t>过程成果报告</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
+          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_b_2026-10-09T07-04-37.png</t>
+          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>1856 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>封面候选底图（非最终交付版本）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -696,22 +696,22 @@
       <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
+          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-07.png</t>
+          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1606 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>封面候选底图（非最终交付版本）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
+          <t>天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>A_professional_portrait_book_c_2026-10-09T06-59-42.png</t>
+          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1546 KB</t>
+          <t>217 KB</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>封面候选底图（非最终交付版本）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -748,22 +748,22 @@
       <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书籍封面.png</t>
+          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>装订打印封面/课题成果汇编-书籍封面.png</t>
+          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>1622 KB</t>
+          <t>289 KB</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>书籍装订印刷素材</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
       <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-书脊.png</t>
+          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>装订打印封面/课题成果汇编-书脊.png</t>
+          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>43 KB</t>
+          <t>307 KB</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>书籍装订印刷素材</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -800,22 +800,22 @@
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-全封展开图.png</t>
+          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>装订打印封面/课题成果汇编-全封展开图.png</t>
+          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>3681 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>书籍装订印刷素材</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -826,22 +826,22 @@
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>课题成果汇编-封底.png</t>
+          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>装订打印封面/课题成果汇编-封底.png</t>
+          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>1895 KB</t>
+          <t>294 KB</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>书籍装订印刷素材</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -849,24 +849,20 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>过程成果报告</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
+          <t>186 KB</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -882,17 +878,17 @@
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>291 KB</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -908,17 +904,17 @@
       <c r="B19" s="4" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>天平街道住宅小区2025年度分析报告.docx</t>
+          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>217 KB</t>
+          <t>301 KB</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -934,17 +930,17 @@
       <c r="B20" s="4" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>289 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -960,17 +956,17 @@
       <c r="B21" s="4" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>307 KB</t>
+          <t>309 KB</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -986,12 +982,12 @@
       <c r="B22" s="4" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1012,17 +1008,17 @@
       <c r="B23" s="4" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>294 KB</t>
+          <t>273 KB</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1038,17 +1034,17 @@
       <c r="B24" s="4" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>186 KB</t>
+          <t>271 KB</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1064,22 +1060,22 @@
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>291 KB</t>
+          <t>250 KB</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1090,22 +1086,22 @@
       <c r="B26" s="4" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>301 KB</t>
+          <t>478 KB</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1116,22 +1112,22 @@
       <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
+          <t>626 KB</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1138,22 @@
       <c r="B28" s="4" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>309 KB</t>
+          <t>104 KB</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1168,22 +1164,22 @@
       <c r="B29" s="4" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>122 KB</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1190,22 @@
       <c r="B30" s="4" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>273 KB</t>
+          <t>117 KB</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1220,22 +1216,22 @@
       <c r="B31" s="4" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>271 KB</t>
+          <t>165 KB</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1246,17 +1242,17 @@
       <c r="B32" s="4" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>20260430 钦州路111弄工单分析报告.docx</t>
+          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
+          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>250 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1272,17 +1268,17 @@
       <c r="B33" s="4" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>478 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1298,17 +1294,17 @@
       <c r="B34" s="4" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>626 KB</t>
+          <t>1343 KB</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1324,17 +1320,17 @@
       <c r="B35" s="4" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>104 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1350,17 +1346,17 @@
       <c r="B36" s="4" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>122 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1376,17 +1372,17 @@
       <c r="B37" s="4" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>117 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1402,17 +1398,17 @@
       <c r="B38" s="4" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>165 KB</t>
+          <t>323 KB</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1428,17 +1424,17 @@
       <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>127 KB</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -1454,17 +1450,17 @@
       <c r="B40" s="4" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>102 KB</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1480,17 +1476,17 @@
       <c r="B41" s="4" t="inlineStr"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1343 KB</t>
+          <t>59 KB</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1506,17 +1502,17 @@
       <c r="B42" s="4" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>2026年7月徐汇区12345工单分析报告.docx</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>102 KB</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1532,17 +1528,17 @@
       <c r="B43" s="4" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>1445 KB</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -1555,25 +1551,29 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>历史版本</t>
+        </is>
+      </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>12256 KB</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>过程版本留档，非最终交付版本</t>
         </is>
       </c>
     </row>
@@ -1584,206 +1584,20 @@
       <c r="B45" s="4" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>323 KB</t>
+          <t>10289 KB</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>127 KB</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>102 KB</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>59 KB</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr"/>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>2026年7月徐汇区12345工单分析报告.docx</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>102 KB</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>1445 KB</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>历史版本</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>12256 KB</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>过程版本留档，非最终交付版本</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>10289 KB</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>过程版本留档，非最终交付版本</t>
         </is>

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 41 个文件；主交付物 1 份 · 电子附件 4 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
+          <t>共 42 个文件；主交付物 2 份 · 电子附件 4 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
         </is>
       </c>
     </row>
@@ -555,29 +555,25 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>电子附件</t>
-        </is>
-      </c>
+      <c r="B6" s="4" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>徐汇区数据赋能下的住宅小区治理与物业服务质量提升探索项目课题成果汇编.pdf</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>附件1_高风险小区评分全量清单.xlsx</t>
+          <t>徐汇区数据赋能下的住宅小区治理与物业服务质量提升探索项目课题成果汇编.pdf</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>19219 KB</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>高风险小区评分全量清单（772 个参评小区）</t>
+          <t>课题成果汇编 PDF 版（打印与分发用，与 Word 版同源）</t>
         </is>
       </c>
     </row>
@@ -585,25 +581,29 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>电子附件</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
+          <t>附件1_高风险小区评分全量清单.xlsx</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>42 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
+          <t>高风险小区评分全量清单（772 个参评小区）</t>
         </is>
       </c>
     </row>
@@ -614,22 +614,22 @@
       <c r="B8" s="4" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>附件3_词云清单.xlsx</t>
+          <t>附件2_2026年1-8月投诉去重建议清单.xlsx</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>26 KB</t>
+          <t>42 KB</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
+          <t>2026 年 1-8 月投诉去重建议清单（逐月明细）</t>
         </is>
       </c>
     </row>
@@ -640,22 +640,22 @@
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>附件4_交付物清单.xlsx</t>
+          <t>附件3_词云清单.xlsx</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>8 KB</t>
+          <t>26 KB</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>交付物清单（本表）</t>
+          <t>13 街镇词云词表（Top24 展示 + 补位候选）</t>
         </is>
       </c>
     </row>
@@ -663,29 +663,25 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>过程成果报告</t>
-        </is>
-      </c>
+      <c r="B10" s="4" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>附件4_交付物清单.xlsx</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
+          <t>8 KB</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
+          <t>交付物清单（本表）</t>
         </is>
       </c>
     </row>
@@ -693,20 +689,24 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>过程成果报告</t>
+        </is>
+      </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/凌云路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -722,17 +722,17 @@
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>天平街道住宅小区2025年度分析报告.docx</t>
+          <t>华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/华泾镇2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>217 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -748,17 +748,17 @@
       <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/天平街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>289 KB</t>
+          <t>217 KB</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -774,17 +774,17 @@
       <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/康健新村街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>307 KB</t>
+          <t>289 KB</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -800,17 +800,17 @@
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/徐家汇街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>307 KB</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -826,17 +826,17 @@
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/徐汇区长桥街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>294 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -852,17 +852,17 @@
       <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/斜土路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>186 KB</t>
+          <t>294 KB</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -878,17 +878,17 @@
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/枫林街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>291 KB</t>
+          <t>186 KB</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -904,17 +904,17 @@
       <c r="B19" s="4" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
+          <t>年度分析报告/街道/湖南路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>301 KB</t>
+          <t>291 KB</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -930,17 +930,17 @@
       <c r="B20" s="4" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/漕河泾街道住宅小区2025年度分析报告.docx</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>299 KB</t>
+          <t>301 KB</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -956,17 +956,17 @@
       <c r="B21" s="4" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/田林街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>309 KB</t>
+          <t>299 KB</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -982,17 +982,17 @@
       <c r="B22" s="4" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/街道/虹梅路街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>300 KB</t>
+          <t>309 KB</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1008,17 +1008,17 @@
       <c r="B23" s="4" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
+          <t>年度分析报告/街道/龙华街道2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>273 KB</t>
+          <t>300 KB</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1034,17 +1034,17 @@
       <c r="B24" s="4" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
+          <t>年度分析报告/集团/城投集团住宅小区2025年度诉求分析报告.docx</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>271 KB</t>
+          <t>273 KB</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1060,22 +1060,22 @@
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>20260430 钦州路111弄工单分析报告.docx</t>
+          <t>徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
+          <t>年度分析报告/集团/徐房集团2025年住宅小区12345投诉工单分析报告.docx</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>250 KB</t>
+          <t>271 KB</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>月度滚动分析成果（19 份）</t>
+          <t>年度分析成果 · 街镇 13 份 + 集团 2 份</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1086,17 @@
       <c r="B26" s="4" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
+          <t>月度分析报告/20260430 钦州路111弄工单分析报告.docx</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>478 KB</t>
+          <t>250 KB</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1112,17 +1112,17 @@
       <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
+          <t>月度分析报告/20260519 2025年徐汇区物业治理工单年度分析报告(2).docx</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>626 KB</t>
+          <t>478 KB</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1138,17 +1138,17 @@
       <c r="B28" s="4" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
+          <t>月度分析报告/20260520 25年及26年1季度区局工单14分类 “满意物业”简报.docx</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>104 KB</t>
+          <t>626 KB</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1164,17 +1164,17 @@
       <c r="B29" s="4" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
+          <t>月度分析报告/20260522 2025-2026年业委会规范化运作类工单分析报告V2.docx</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>122 KB</t>
+          <t>104 KB</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1190,17 +1190,17 @@
       <c r="B30" s="4" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年停车管理类工单分析报告V3.docx</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>117 KB</t>
+          <t>122 KB</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1216,17 +1216,17 @@
       <c r="B31" s="4" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年垃圾清理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>165 KB</t>
+          <t>117 KB</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1242,17 +1242,17 @@
       <c r="B32" s="4" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
+          <t>月度分析报告/20260522 2025-2026年物业日常管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>23 KB</t>
+          <t>165 KB</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1268,17 +1268,17 @@
       <c r="B33" s="4" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
+          <t>月度分析报告/20260610徐汇区防汛防台工单数据分析报告.docx</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>23 KB</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1294,17 +1294,17 @@
       <c r="B34" s="4" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
+          <t>月度分析报告/20260616 徐汇区工单数据集中分析报告.docx</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1343 KB</t>
+          <t>16 KB</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1320,17 +1320,17 @@
       <c r="B35" s="4" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
+          <t>月度分析报告/20260617市局14类1-5月停车管理工单分析.docx</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>25 KB</t>
+          <t>1343 KB</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1346,17 +1346,17 @@
       <c r="B36" s="4" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
+          <t>月度分析报告/20260710 1-6月停车管理类工单分析报告.docx</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>25 KB</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1372,17 +1372,17 @@
       <c r="B37" s="4" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
+          <t>月度分析报告/20260710 （夏令热线材料）居民投诉重点热点问题及特色工作_2026.docx</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>41 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1398,17 +1398,17 @@
       <c r="B38" s="4" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
+          <t>月度分析报告/20260728 徐汇区重复投诉工单分析报告_2026年1-6月.docx</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>323 KB</t>
+          <t>41 KB</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1424,17 +1424,17 @@
       <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
+          <t>20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
+          <t>月度分析报告/20260804 2026年徐汇区防汛防台工单分析报告.docx</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>127 KB</t>
+          <t>323 KB</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="B40" s="4" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
+          <t>2026年3月徐汇区12345工单分析报告_v7.docx</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
+          <t>月度分析报告/2026年3月徐汇区12345工单分析报告_v7.docx</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>102 KB</t>
+          <t>127 KB</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1476,17 +1476,17 @@
       <c r="B41" s="4" t="inlineStr"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
+          <t>2026年4月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
+          <t>月度分析报告/2026年4月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>59 KB</t>
+          <t>102 KB</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1502,17 +1502,17 @@
       <c r="B42" s="4" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2026年7月徐汇区12345工单分析报告.docx</t>
+          <t>2026年5月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
+          <t>月度分析报告/2026年5月徐汇区12345工单分析报告_v1.docx</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>102 KB</t>
+          <t>59 KB</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1528,17 +1528,17 @@
       <c r="B43" s="4" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+          <t>2026年7月徐汇区12345工单分析报告.docx</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
+          <t>月度分析报告/2026年7月徐汇区12345工单分析报告.docx</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>1445 KB</t>
+          <t>102 KB</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -1551,29 +1551,25 @@
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>历史版本</t>
-        </is>
-      </c>
+      <c r="B44" s="4" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+          <t>徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+          <t>月度分析报告/徐汇区住宅小区2025年度物业管理分析报告 0409.docx</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>12256 KB</t>
+          <t>1445 KB</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>过程版本留档，非最终交付版本</t>
+          <t>月度滚动分析成果（19 份）</t>
         </is>
       </c>
     </row>
@@ -1581,23 +1577,53 @@
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>历史版本</t>
+        </is>
+      </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
+          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>12256 KB</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>过程版本留档，非最终交付版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
           <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>10289 KB</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>过程版本留档，非最终交付版本</t>
         </is>

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>10317 KB</t>
+          <t>10318 KB</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>19219 KB</t>
+          <t>19248 KB</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>10318 KB</t>
+          <t>10319 KB</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>19248 KB</t>
+          <t>19256 KB</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 42 个文件；主交付物 2 份 · 电子附件 4 份 · 过程成果报告 34 份 · 历史版本 2 份</t>
+          <t>共 40 个文件；主交付物 2 份 · 电子附件 4 份 · 过程成果报告 34 份</t>
         </is>
       </c>
     </row>
@@ -1570,62 +1570,6 @@
       <c r="F44" s="5" t="inlineStr">
         <is>
           <t>月度滚动分析成果（19 份）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>历史版本</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编-人工修改版.docx</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>12256 KB</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>过程版本留档，非最终交付版本</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>_archive/徐汇区物业投诉治理数字化分析课题（一期）成果汇编.docx</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>10289 KB</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>过程版本留档，非最终交付版本</t>
         </is>
       </c>
     </row>

--- a/交付物/附件4_交付物清单.xlsx
+++ b/交付物/附件4_交付物清单.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>19256 KB</t>
+          <t>19255 KB</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
